--- a/data/manpower_resources.xlsx
+++ b/data/manpower_resources.xlsx
@@ -1,103 +1,58 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sahil2.Qureshi\Documents\Project_Planner_SHP\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF7A644D-CC6E-4E55-8118-3EE8FA16258E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14380" windowHeight="4590" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Machine Status" sheetId="1" r:id="rId1"/>
-    <sheet name="Manpower Status" sheetId="2" r:id="rId2"/>
-    <sheet name="Shifthour Status" sheetId="3" r:id="rId3"/>
+    <sheet name="Machine Status" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Manpower Status" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Manhour Status" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="12">
-  <si>
-    <t>Shift Date</t>
-  </si>
-  <si>
-    <t>Machine Type</t>
-  </si>
-  <si>
-    <t>Machines Available</t>
-  </si>
-  <si>
-    <t>12-Jun-2026</t>
-  </si>
-  <si>
-    <t>Hammer</t>
-  </si>
-  <si>
-    <t>13-Jun-2026</t>
-  </si>
-  <si>
-    <t>15-Jun-2026</t>
-  </si>
-  <si>
-    <t>16-Jun-2026</t>
-  </si>
-  <si>
-    <t>17-Jun-2026</t>
-  </si>
-  <si>
-    <t>18-Jun-2026</t>
-  </si>
-  <si>
-    <t>Manpower Available</t>
-  </si>
-  <si>
-    <t>Manhour</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <name val="Arial"/>
       <sz val="10"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E79"/>
+        <fgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD6E4F0"/>
+        <fgColor rgb="00D6E4F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -111,60 +66,118 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB0B0B0"/>
+        <color rgb="00B0B0B0"/>
       </left>
       <right style="thin">
-        <color rgb="FFB0B0B0"/>
+        <color rgb="00B0B0B0"/>
       </right>
       <top style="thin">
-        <color rgb="FFB0B0B0"/>
+        <color rgb="00B0B0B0"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB0B0B0"/>
+        <color rgb="00B0B0B0"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -452,100 +465,332 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="21" customWidth="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Shift Date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Machine Type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Machines Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>12-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>13-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B2" s="3" t="s">
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>15-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>15-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="C2" s="4">
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>16-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>17-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>18-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>19-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>20-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>21-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>23-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>24-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>25-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>26-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>29-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>30-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B3" s="6" t="s">
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>01-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="C3" s="7">
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>02-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="3" t="s">
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>03-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="n">
         <v>4</v>
-      </c>
-      <c r="C4" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="4">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -554,76 +799,218 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="21" customWidth="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="4">
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Shift Date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Manpower Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>12-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="7">
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>13-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n">
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="4">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>15-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="7">
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>15-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="4">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>16-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="7">
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>17-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="4">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>18-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
         <v>27</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>19-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>20-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>23-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>24-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>25-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>26-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>29-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>30-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>01-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>02-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>03-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -632,74 +1019,217 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="16" customWidth="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="4">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="7">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="4">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="7">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="4">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="7">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="4">
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Shift Date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Manhour</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>12-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>13-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>15-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>15-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>16-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>17-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>18-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>19-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>20-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>22-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>23-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>24-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>25-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>26-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>29-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>30-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>01-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>02-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>03-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
         <v>9</v>
       </c>
     </row>

--- a/data/manpower_resources.xlsx
+++ b/data/manpower_resources.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Machine Status" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Manpower Status" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Manhour Status" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Machine Status" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manpower Status" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manhour Status" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>12-Jun-2026</t>
+          <t>15-Jun-2026</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -513,7 +513,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>13-Jun-2026</t>
+          <t>15-Jun-2026</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
@@ -522,13 +522,13 @@
         </is>
       </c>
       <c r="C3" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -552,13 +552,13 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -567,13 +567,13 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -582,13 +582,13 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>20-Jun-2026</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -597,13 +597,13 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>19-Jun-2026</t>
+          <t>21-Jun-2026</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -611,14 +611,12 @@
           <t>Hammer</t>
         </is>
       </c>
-      <c r="C9" s="7" t="n">
-        <v>2</v>
-      </c>
+      <c r="C9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>20-Jun-2026</t>
+          <t>22-Jun-2026</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -633,7 +631,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>21-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -641,12 +639,14 @@
           <t>Hammer</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n"/>
+      <c r="C11" s="7" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>24-Jun-2026</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -661,7 +661,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>23-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -670,13 +670,13 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>26-Jun-2026</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -691,7 +691,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>25-Jun-2026</t>
+          <t>29-Jun-2026</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -700,13 +700,13 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>26-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>01-Jul-2026</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -736,7 +736,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>30-Jun-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -745,13 +745,13 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -766,7 +766,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>10-Jul-2026</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -775,13 +775,13 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>12-Jul-2026</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -790,7 +790,22 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>13-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -804,7 +819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -826,17 +841,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>12-Jun-2026</t>
+          <t>15-Jun-2026</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>13-Jun-2026</t>
+          <t>15-Jun-2026</t>
         </is>
       </c>
       <c r="B3" s="7" t="n">
@@ -846,37 +861,37 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
@@ -886,37 +901,37 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>20-Jun-2026</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>19-Jun-2026</t>
+          <t>22-Jun-2026</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>20-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>24-Jun-2026</t>
         </is>
       </c>
       <c r="B11" s="7" t="n">
@@ -926,7 +941,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>23-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
@@ -936,7 +951,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>26-Jun-2026</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
@@ -946,71 +961,81 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>25-Jun-2026</t>
+          <t>29-Jun-2026</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>26-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>01-Jul-2026</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>30-Jun-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>10-Jul-2026</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>12-Jul-2026</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>34</v>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>13-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1024,7 +1049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1046,7 +1071,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>12-Jun-2026</t>
+          <t>15-Jun-2026</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
@@ -1056,7 +1081,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>13-Jun-2026</t>
+          <t>15-Jun-2026</t>
         </is>
       </c>
       <c r="B3" s="7" t="n">
@@ -1066,7 +1091,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>16-Jun-2026</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
@@ -1076,7 +1101,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="B5" s="7" t="n">
@@ -1086,7 +1111,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
@@ -1096,7 +1121,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>19-Jun-2026</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
@@ -1106,7 +1131,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>20-Jun-2026</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
@@ -1116,7 +1141,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>19-Jun-2026</t>
+          <t>22-Jun-2026</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
@@ -1126,7 +1151,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>20-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
@@ -1136,7 +1161,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>24-Jun-2026</t>
         </is>
       </c>
       <c r="B11" s="7" t="n">
@@ -1146,7 +1171,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>23-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
@@ -1156,7 +1181,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>26-Jun-2026</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
@@ -1166,7 +1191,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>25-Jun-2026</t>
+          <t>29-Jun-2026</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
@@ -1176,7 +1201,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>26-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
@@ -1186,7 +1211,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>01-Jul-2026</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
@@ -1196,7 +1221,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>30-Jun-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
@@ -1206,7 +1231,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
@@ -1216,7 +1241,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>10-Jul-2026</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
@@ -1226,10 +1251,20 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>12-Jul-2026</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>13-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n">
         <v>9</v>
       </c>
     </row>

--- a/data/manpower_resources.xlsx
+++ b/data/manpower_resources.xlsx
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -513,7 +513,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>24-Jun-2026</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
@@ -522,13 +522,13 @@
         </is>
       </c>
       <c r="C3" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>26-Jun-2026</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -552,13 +552,13 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>29-Jun-2026</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -567,13 +567,13 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>19-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -582,13 +582,13 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>20-Jun-2026</t>
+          <t>01-Jul-2026</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -597,13 +597,13 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>21-Jun-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -611,12 +611,14 @@
           <t>Hammer</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n"/>
+      <c r="C9" s="7" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -625,13 +627,13 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>23-Jun-2026</t>
+          <t>10-Jul-2026</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -640,13 +642,13 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>12-Jul-2026</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -655,13 +657,13 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>25-Jun-2026</t>
+          <t>13-Jul-2026</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -676,7 +678,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>26-Jun-2026</t>
+          <t>14-Jul-2026</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -685,13 +687,13 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -700,13 +702,13 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>30-Jun-2026</t>
+          <t>17-Jul-2026</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -721,7 +723,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>18-Jul-2026</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -736,7 +738,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>19-Jul-2026</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -745,13 +747,13 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>20-Jul-2026</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -766,7 +768,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>10-Jul-2026</t>
+          <t>21-Jul-2026</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -776,36 +778,6 @@
       </c>
       <c r="C20" s="4" t="n">
         <v>4</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>Hammer</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>13-Jul-2026</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Hammer</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -819,7 +791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -841,107 +813,107 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>24-Jun-2026</t>
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>26-Jun-2026</t>
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>29-Jun-2026</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>19-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>20-Jun-2026</t>
+          <t>01-Jul-2026</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>23-Jun-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>10-Jul-2026</t>
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>25-Jun-2026</t>
+          <t>12-Jul-2026</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
@@ -951,7 +923,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>26-Jun-2026</t>
+          <t>13-Jul-2026</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
@@ -961,81 +933,71 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>14-Jul-2026</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>30-Jun-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>17-Jul-2026</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>18-Jul-2026</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>19-Jul-2026</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>10-Jul-2026</t>
+          <t>20-Jul-2026</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>21-Jul-2026</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>13-Jul-2026</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1049,7 +1011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1071,7 +1033,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
@@ -1081,7 +1043,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>24-Jun-2026</t>
         </is>
       </c>
       <c r="B3" s="7" t="n">
@@ -1091,7 +1053,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>16-Jun-2026</t>
+          <t>25-Jun-2026</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
@@ -1101,7 +1063,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>26-Jun-2026</t>
         </is>
       </c>
       <c r="B5" s="7" t="n">
@@ -1111,7 +1073,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>29-Jun-2026</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
@@ -1121,7 +1083,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>19-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
@@ -1131,7 +1093,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>20-Jun-2026</t>
+          <t>01-Jul-2026</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
@@ -1141,7 +1103,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
@@ -1151,7 +1113,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>23-Jun-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
@@ -1161,7 +1123,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>10-Jul-2026</t>
         </is>
       </c>
       <c r="B11" s="7" t="n">
@@ -1171,7 +1133,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>25-Jun-2026</t>
+          <t>12-Jul-2026</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
@@ -1181,7 +1143,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>26-Jun-2026</t>
+          <t>13-Jul-2026</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
@@ -1191,7 +1153,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>14-Jul-2026</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
@@ -1201,7 +1163,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>30-Jun-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
@@ -1211,7 +1173,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>17-Jul-2026</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
@@ -1221,7 +1183,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>18-Jul-2026</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
@@ -1231,7 +1193,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>19-Jul-2026</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
@@ -1241,7 +1203,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>10-Jul-2026</t>
+          <t>20-Jul-2026</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
@@ -1251,20 +1213,10 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>21-Jul-2026</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>13-Jul-2026</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="n">
         <v>9</v>
       </c>
     </row>

--- a/data/manpower_resources.xlsx
+++ b/data/manpower_resources.xlsx
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>23-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -507,13 +507,13 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>01-Jul-2026</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
@@ -522,13 +522,13 @@
         </is>
       </c>
       <c r="C3" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>25-Jun-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -543,7 +543,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>26-Jun-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -552,13 +552,13 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>10-Jul-2026</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -573,7 +573,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>30-Jun-2026</t>
+          <t>12-Jul-2026</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -582,13 +582,13 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>13-Jul-2026</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -597,13 +597,13 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>14-Jul-2026</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -618,7 +618,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -627,13 +627,13 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>10-Jul-2026</t>
+          <t>17-Jul-2026</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>18-Jul-2026</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>13-Jul-2026</t>
+          <t>19-Jul-2026</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -672,13 +672,13 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>14-Jul-2026</t>
+          <t>20-Jul-2026</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>15-Jul-2026</t>
+          <t>21-Jul-2026</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -702,13 +702,13 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>17-Jul-2026</t>
+          <t>22-Jul-2026</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>18-Jul-2026</t>
+          <t>23-Jul-2026</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -732,13 +732,13 @@
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>19-Jul-2026</t>
+          <t>24-Jul-2026</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -747,13 +747,13 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>20-Jul-2026</t>
+          <t>25-Jul-2026</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -762,13 +762,13 @@
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>21-Jul-2026</t>
+          <t>26-Jul-2026</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -777,7 +777,37 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>27-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>28-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -791,7 +821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -813,191 +843,211 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>23-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>01-Jul-2026</t>
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>25-Jun-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>26-Jun-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>10-Jul-2026</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>30-Jun-2026</t>
+          <t>12-Jul-2026</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>13-Jul-2026</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>14-Jul-2026</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>10-Jul-2026</t>
+          <t>17-Jul-2026</t>
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>18-Jul-2026</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>13-Jul-2026</t>
+          <t>19-Jul-2026</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>14-Jul-2026</t>
+          <t>20-Jul-2026</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>15-Jul-2026</t>
+          <t>21-Jul-2026</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>17-Jul-2026</t>
+          <t>22-Jul-2026</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>18-Jul-2026</t>
+          <t>23-Jul-2026</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>19-Jul-2026</t>
+          <t>24-Jul-2026</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>20-Jul-2026</t>
+          <t>25-Jul-2026</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>21-Jul-2026</t>
+          <t>26-Jul-2026</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>39</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>27-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>28-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1011,7 +1061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1033,7 +1083,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>23-Jun-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
@@ -1043,7 +1093,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>01-Jul-2026</t>
         </is>
       </c>
       <c r="B3" s="7" t="n">
@@ -1053,7 +1103,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>25-Jun-2026</t>
+          <t>02-Jul-2026</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
@@ -1063,7 +1113,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>26-Jun-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="B5" s="7" t="n">
@@ -1073,7 +1123,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>10-Jul-2026</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
@@ -1083,7 +1133,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>30-Jun-2026</t>
+          <t>12-Jul-2026</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
@@ -1093,7 +1143,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>13-Jul-2026</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
@@ -1103,7 +1153,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>02-Jul-2026</t>
+          <t>14-Jul-2026</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
@@ -1113,7 +1163,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
@@ -1123,7 +1173,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>10-Jul-2026</t>
+          <t>17-Jul-2026</t>
         </is>
       </c>
       <c r="B11" s="7" t="n">
@@ -1133,7 +1183,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>18-Jul-2026</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
@@ -1143,7 +1193,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>13-Jul-2026</t>
+          <t>19-Jul-2026</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
@@ -1153,7 +1203,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>14-Jul-2026</t>
+          <t>20-Jul-2026</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
@@ -1163,7 +1213,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>15-Jul-2026</t>
+          <t>21-Jul-2026</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
@@ -1173,7 +1223,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>17-Jul-2026</t>
+          <t>22-Jul-2026</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
@@ -1183,7 +1233,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>18-Jul-2026</t>
+          <t>23-Jul-2026</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
@@ -1193,7 +1243,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>19-Jul-2026</t>
+          <t>24-Jul-2026</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
@@ -1203,7 +1253,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>20-Jul-2026</t>
+          <t>25-Jul-2026</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
@@ -1213,10 +1263,30 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>21-Jul-2026</t>
+          <t>26-Jul-2026</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>27-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>28-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
         <v>9</v>
       </c>
     </row>
